--- a/Data/Beaver_Creek_Solution.xlsx
+++ b/Data/Beaver_Creek_Solution.xlsx
@@ -846,7 +846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="true"/>
